--- a/leads_jercol_rest.xlsx
+++ b/leads_jercol_rest.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -535,14 +535,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LEADS - RESTAURANTES EN MONTERIA COLOMBIA - 26/03/2026</t>
+          <t>LEADS - RESTAURANTES EN MONTERIA COLOMBIA - 27/03/2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total encontrados: 3  |  Con WhatsApp confirmado: 1  |  WhatsApp probable: 2  |  Generado por Jercol Technologies</t>
+          <t>Total encontrados: 4  |  Con WhatsApp confirmado: 2  |  WhatsApp probable: 2  |  Generado por Jercol Technologies</t>
         </is>
       </c>
     </row>
@@ -735,6 +735,52 @@
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Los Potrillos Restaurante-Bar</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Restaurante familiar</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>3105974885</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Km 59+700 RN 7401, Montería, Córdoba</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lospotrillosrestaurantebar</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -751,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -884,6 +930,36 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Los Potrillos Restaurante-Bar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3105974885</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Km 59+700 RN 7401, Montería, Córdoba</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lospotrillosrestaurantebar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_jercol_rest.xlsx
+++ b/leads_jercol_rest.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -542,7 +542,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total encontrados: 4  |  Con WhatsApp confirmado: 2  |  WhatsApp probable: 2  |  Generado por Jercol Technologies</t>
+          <t>Total encontrados: 6  |  Con WhatsApp confirmado: 2  |  WhatsApp probable: 4  |  Generado por Jercol Technologies</t>
         </is>
       </c>
     </row>
@@ -781,6 +781,98 @@
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>El Portón Parrilla</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>3212281671</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>PROBABLE</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Cra. 14 #No. 34A-10, Montería, Córdoba</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Restaurante El Bocachico Elegante</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>3045929761</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>PROBABLE</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Carrera 7 No. 32-67 Centro, Montería, Córdoba</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -797,7 +889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -960,6 +1052,66 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>El Portón Parrilla</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3212281671</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PROBABLE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cra. 14 #No. 34A-10, Montería, Córdoba</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Restaurante El Bocachico Elegante</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3045929761</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PROBABLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Carrera 7 No. 32-67 Centro, Montería, Córdoba</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
